--- a/dataset_fiis_2019_2024.xlsx
+++ b/dataset_fiis_2019_2024.xlsx
@@ -505,7 +505,7 @@
         <v>0.0083</v>
       </c>
       <c r="I2" t="n">
-        <v>83.244962</v>
+        <v>8324.4962</v>
       </c>
     </row>
     <row r="3">
@@ -538,7 +538,7 @@
         <v>0.0103</v>
       </c>
       <c r="I3" t="n">
-        <v>84.048225</v>
+        <v>8404.8225</v>
       </c>
     </row>
     <row r="4">
@@ -571,7 +571,7 @@
         <v>0.0102</v>
       </c>
       <c r="I4" t="n">
-        <v>83.742503</v>
+        <v>8374.2503</v>
       </c>
     </row>
     <row r="5">
@@ -604,7 +604,7 @@
         <v>0.0103</v>
       </c>
       <c r="I5" t="n">
-        <v>83.00784299999999</v>
+        <v>8300.784299999999</v>
       </c>
     </row>
     <row r="6">
@@ -637,7 +637,7 @@
         <v>0.0117</v>
       </c>
       <c r="I6" t="n">
-        <v>83.92501799999999</v>
+        <v>8392.5018</v>
       </c>
     </row>
     <row r="7">
@@ -670,7 +670,7 @@
         <v>0.0107</v>
       </c>
       <c r="I7" t="n">
-        <v>85.166286</v>
+        <v>8516.6286</v>
       </c>
     </row>
     <row r="8">
@@ -703,7 +703,7 @@
         <v>0.0102</v>
       </c>
       <c r="I8" t="n">
-        <v>86.215993</v>
+        <v>8621.5993</v>
       </c>
     </row>
     <row r="9">
@@ -736,7 +736,7 @@
         <v>0.0102</v>
       </c>
       <c r="I9" t="n">
-        <v>85.532411</v>
+        <v>8553.241099999999</v>
       </c>
     </row>
     <row r="10">
@@ -769,7 +769,7 @@
         <v>0.0112</v>
       </c>
       <c r="I10" t="n">
-        <v>85.36599200000001</v>
+        <v>8536.599200000001</v>
       </c>
     </row>
     <row r="11">
@@ -802,7 +802,7 @@
         <v>0.0112</v>
       </c>
       <c r="I11" t="n">
-        <v>85.365269</v>
+        <v>8536.526900000001</v>
       </c>
     </row>
     <row r="12">
@@ -835,7 +835,7 @@
         <v>0.0092</v>
       </c>
       <c r="I12" t="n">
-        <v>86.45939199999999</v>
+        <v>8645.939200000001</v>
       </c>
     </row>
     <row r="13">
@@ -868,7 +868,7 @@
         <v>0.0117</v>
       </c>
       <c r="I13" t="n">
-        <v>88.76237999999999</v>
+        <v>8876.237999999999</v>
       </c>
     </row>
     <row r="14">
@@ -901,7 +901,7 @@
         <v>0.0092</v>
       </c>
       <c r="I14" t="n">
-        <v>90.555673</v>
+        <v>9055.567300000001</v>
       </c>
     </row>
     <row r="15">
@@ -934,7 +934,7 @@
         <v>0.0112</v>
       </c>
       <c r="I15" t="n">
-        <v>91.966838</v>
+        <v>9196.683800000001</v>
       </c>
     </row>
     <row r="16">
@@ -1556,7 +1556,7 @@
         <v>0.0028</v>
       </c>
       <c r="I35" t="n">
-        <v>72.50940199999999</v>
+        <v>7250.9402</v>
       </c>
     </row>
     <row r="36">
@@ -1589,7 +1589,7 @@
         <v>0.0024</v>
       </c>
       <c r="I36" t="n">
-        <v>73.610365</v>
+        <v>7361.0365</v>
       </c>
     </row>
     <row r="37">
@@ -1622,7 +1622,7 @@
         <v>0.0021</v>
       </c>
       <c r="I37" t="n">
-        <v>75.11804100000001</v>
+        <v>7511.8041</v>
       </c>
     </row>
     <row r="38">
@@ -1655,7 +1655,7 @@
         <v>0.0019</v>
       </c>
       <c r="I38" t="n">
-        <v>78.412774</v>
+        <v>7841.2774</v>
       </c>
     </row>
     <row r="39">
@@ -1688,7 +1688,7 @@
         <v>0.0016</v>
       </c>
       <c r="I39" t="n">
-        <v>77.00332899999999</v>
+        <v>7700.3329</v>
       </c>
     </row>
     <row r="40">
@@ -1721,7 +1721,7 @@
         <v>0.0016</v>
       </c>
       <c r="I40" t="n">
-        <v>75.83918799999999</v>
+        <v>7583.9188</v>
       </c>
     </row>
     <row r="41">
@@ -1754,7 +1754,7 @@
         <v>0.0016</v>
       </c>
       <c r="I41" t="n">
-        <v>75.999932</v>
+        <v>7599.9932</v>
       </c>
     </row>
     <row r="42">
@@ -1787,7 +1787,7 @@
         <v>0.0015</v>
       </c>
       <c r="I42" t="n">
-        <v>77.519738</v>
+        <v>7751.9738</v>
       </c>
     </row>
     <row r="43">
@@ -1820,7 +1820,7 @@
         <v>0.0083</v>
       </c>
       <c r="I43" t="n">
-        <v>83.244962</v>
+        <v>8324.4962</v>
       </c>
     </row>
     <row r="44">
@@ -1853,7 +1853,7 @@
         <v>0.0103</v>
       </c>
       <c r="I44" t="n">
-        <v>84.048225</v>
+        <v>8404.8225</v>
       </c>
     </row>
     <row r="45">
@@ -1886,7 +1886,7 @@
         <v>0.0102</v>
       </c>
       <c r="I45" t="n">
-        <v>83.742503</v>
+        <v>8374.2503</v>
       </c>
     </row>
     <row r="46">
@@ -1919,7 +1919,7 @@
         <v>0.0103</v>
       </c>
       <c r="I46" t="n">
-        <v>83.00784299999999</v>
+        <v>8300.784299999999</v>
       </c>
     </row>
     <row r="47">
@@ -1952,7 +1952,7 @@
         <v>0.0117</v>
       </c>
       <c r="I47" t="n">
-        <v>83.92501799999999</v>
+        <v>8392.5018</v>
       </c>
     </row>
     <row r="48">
@@ -1985,7 +1985,7 @@
         <v>0.0107</v>
       </c>
       <c r="I48" t="n">
-        <v>85.166286</v>
+        <v>8516.6286</v>
       </c>
     </row>
     <row r="49">
@@ -2018,7 +2018,7 @@
         <v>0.0102</v>
       </c>
       <c r="I49" t="n">
-        <v>86.215993</v>
+        <v>8621.5993</v>
       </c>
     </row>
     <row r="50">
@@ -2051,7 +2051,7 @@
         <v>0.0102</v>
       </c>
       <c r="I50" t="n">
-        <v>85.532411</v>
+        <v>8553.241099999999</v>
       </c>
     </row>
     <row r="51">
@@ -2084,7 +2084,7 @@
         <v>0.0112</v>
       </c>
       <c r="I51" t="n">
-        <v>85.36599200000001</v>
+        <v>8536.599200000001</v>
       </c>
     </row>
     <row r="52">
@@ -2117,7 +2117,7 @@
         <v>0.0112</v>
       </c>
       <c r="I52" t="n">
-        <v>85.365269</v>
+        <v>8536.526900000001</v>
       </c>
     </row>
     <row r="53">
@@ -2150,7 +2150,7 @@
         <v>0.0092</v>
       </c>
       <c r="I53" t="n">
-        <v>86.45939199999999</v>
+        <v>8645.939200000001</v>
       </c>
     </row>
     <row r="54">
@@ -2183,7 +2183,7 @@
         <v>0.0117</v>
       </c>
       <c r="I54" t="n">
-        <v>88.76237999999999</v>
+        <v>8876.237999999999</v>
       </c>
     </row>
     <row r="55">
@@ -2216,7 +2216,7 @@
         <v>0.0092</v>
       </c>
       <c r="I55" t="n">
-        <v>90.555673</v>
+        <v>9055.567300000001</v>
       </c>
     </row>
     <row r="56">
@@ -2249,7 +2249,7 @@
         <v>0.0112</v>
       </c>
       <c r="I56" t="n">
-        <v>91.966838</v>
+        <v>9196.683800000001</v>
       </c>
     </row>
     <row r="57">
@@ -2840,7 +2840,7 @@
         <v>0.0054</v>
       </c>
       <c r="I75" t="n">
-        <v>69.000861</v>
+        <v>6900.086</v>
       </c>
     </row>
     <row r="76">
@@ -2873,7 +2873,7 @@
         <v>0.0047</v>
       </c>
       <c r="I76" t="n">
-        <v>71.577665</v>
+        <v>7157.7665</v>
       </c>
     </row>
     <row r="77">
@@ -2906,7 +2906,7 @@
         <v>0.0057</v>
       </c>
       <c r="I77" t="n">
-        <v>72.499047</v>
+        <v>7249.9047</v>
       </c>
     </row>
     <row r="78">
@@ -2939,7 +2939,7 @@
         <v>0.005</v>
       </c>
       <c r="I78" t="n">
-        <v>72.207688</v>
+        <v>7220.7688</v>
       </c>
     </row>
     <row r="79">
@@ -2972,7 +2972,7 @@
         <v>0.0046</v>
       </c>
       <c r="I79" t="n">
-        <v>74.27373</v>
+        <v>7427.373</v>
       </c>
     </row>
     <row r="80">
@@ -3005,7 +3005,7 @@
         <v>0.0048</v>
       </c>
       <c r="I80" t="n">
-        <v>76.771331</v>
+        <v>7677.1331</v>
       </c>
     </row>
     <row r="81">
@@ -3038,7 +3038,7 @@
         <v>0.0038</v>
       </c>
       <c r="I81" t="n">
-        <v>74.886931</v>
+        <v>7488.6931</v>
       </c>
     </row>
     <row r="82">
@@ -3071,7 +3071,7 @@
         <v>0.0037</v>
       </c>
       <c r="I82" t="n">
-        <v>76.388847</v>
+        <v>7638.8847</v>
       </c>
     </row>
     <row r="83">
@@ -3104,7 +3104,7 @@
         <v>0.0038</v>
       </c>
       <c r="I83" t="n">
-        <v>76.588494</v>
+        <v>7658.8494</v>
       </c>
     </row>
     <row r="84">
@@ -3137,7 +3137,7 @@
         <v>0.0029</v>
       </c>
       <c r="I84" t="n">
-        <v>76.932687</v>
+        <v>7693.2687</v>
       </c>
     </row>
     <row r="85">
@@ -3170,7 +3170,7 @@
         <v>0.0034</v>
       </c>
       <c r="I85" t="n">
-        <v>71.568826</v>
+        <v>7156.8826</v>
       </c>
     </row>
     <row r="86">
@@ -3203,7 +3203,7 @@
         <v>0.0028</v>
       </c>
       <c r="I86" t="n">
-        <v>72.50940199999999</v>
+        <v>7250.9402</v>
       </c>
     </row>
     <row r="87">
@@ -3236,7 +3236,7 @@
         <v>0.0024</v>
       </c>
       <c r="I87" t="n">
-        <v>73.610365</v>
+        <v>7361.0365</v>
       </c>
     </row>
     <row r="88">
@@ -3269,7 +3269,7 @@
         <v>0.0021</v>
       </c>
       <c r="I88" t="n">
-        <v>75.11804100000001</v>
+        <v>7511.8041</v>
       </c>
     </row>
     <row r="89">
@@ -3302,7 +3302,7 @@
         <v>0.0019</v>
       </c>
       <c r="I89" t="n">
-        <v>78.412774</v>
+        <v>7841.2774</v>
       </c>
     </row>
     <row r="90">
@@ -3335,7 +3335,7 @@
         <v>0.0016</v>
       </c>
       <c r="I90" t="n">
-        <v>77.00332899999999</v>
+        <v>7700.3329</v>
       </c>
     </row>
     <row r="91">
@@ -3368,7 +3368,7 @@
         <v>0.0016</v>
       </c>
       <c r="I91" t="n">
-        <v>75.83918799999999</v>
+        <v>7583.9188</v>
       </c>
     </row>
     <row r="92">
@@ -3401,7 +3401,7 @@
         <v>0.0016</v>
       </c>
       <c r="I92" t="n">
-        <v>75.999932</v>
+        <v>7599.9932</v>
       </c>
     </row>
     <row r="93">
@@ -3434,7 +3434,7 @@
         <v>0.0015</v>
       </c>
       <c r="I93" t="n">
-        <v>77.519738</v>
+        <v>7751.9738</v>
       </c>
     </row>
     <row r="94">
@@ -3467,7 +3467,7 @@
         <v>0.0016</v>
       </c>
       <c r="I94" t="n">
-        <v>81.282014</v>
+        <v>8128.2014</v>
       </c>
     </row>
     <row r="95">
@@ -3500,7 +3500,7 @@
         <v>0.0015</v>
       </c>
       <c r="I95" t="n">
-        <v>80.589941</v>
+        <v>8058.9941</v>
       </c>
     </row>
     <row r="96">
@@ -3533,7 +3533,7 @@
         <v>0.0013</v>
       </c>
       <c r="I96" t="n">
-        <v>79.36756</v>
+        <v>7936.756</v>
       </c>
     </row>
     <row r="97">
@@ -3566,7 +3566,7 @@
         <v>0.002</v>
       </c>
       <c r="I97" t="n">
-        <v>79.00167500000001</v>
+        <v>7900.1675</v>
       </c>
     </row>
     <row r="98">
@@ -3599,7 +3599,7 @@
         <v>0.0021</v>
       </c>
       <c r="I98" t="n">
-        <v>79.516036</v>
+        <v>7951.6036</v>
       </c>
     </row>
     <row r="99">
@@ -3632,7 +3632,7 @@
         <v>0.0027</v>
       </c>
       <c r="I99" t="n">
-        <v>80.357348</v>
+        <v>8035.7348</v>
       </c>
     </row>
     <row r="100">
@@ -3665,7 +3665,7 @@
         <v>0.0031</v>
       </c>
       <c r="I100" t="n">
-        <v>80.695116</v>
+        <v>8069.5116</v>
       </c>
     </row>
     <row r="101">
@@ -3698,7 +3698,7 @@
         <v>0.0036</v>
       </c>
       <c r="I101" t="n">
-        <v>80.393818</v>
+        <v>8039.3818</v>
       </c>
     </row>
     <row r="102">
@@ -3731,7 +3731,7 @@
         <v>0.0043</v>
       </c>
       <c r="I102" t="n">
-        <v>79.517839</v>
+        <v>7951.7839</v>
       </c>
     </row>
     <row r="103">
@@ -3764,7 +3764,7 @@
         <v>0.0044</v>
       </c>
       <c r="I103" t="n">
-        <v>79.412036</v>
+        <v>7941.2036</v>
       </c>
     </row>
     <row r="104">
@@ -3797,7 +3797,7 @@
         <v>0.0049</v>
       </c>
       <c r="I104" t="n">
-        <v>77.391648</v>
+        <v>7739.1648</v>
       </c>
     </row>
     <row r="105">
@@ -3830,7 +3830,7 @@
         <v>0.0059</v>
       </c>
       <c r="I105" t="n">
-        <v>80.074422</v>
+        <v>8007.4422</v>
       </c>
     </row>
     <row r="106">
@@ -3863,7 +3863,7 @@
         <v>0.0077</v>
       </c>
       <c r="I106" t="n">
-        <v>80.216174</v>
+        <v>8021.6174</v>
       </c>
     </row>
     <row r="107">
@@ -3896,7 +3896,7 @@
         <v>0.0073</v>
       </c>
       <c r="I107" t="n">
-        <v>79.665268</v>
+        <v>7966.5268</v>
       </c>
     </row>
     <row r="108">
@@ -3929,7 +3929,7 @@
         <v>0.0076</v>
       </c>
       <c r="I108" t="n">
-        <v>80.099069</v>
+        <v>8009.9069</v>
       </c>
     </row>
     <row r="109">
@@ -3962,7 +3962,7 @@
         <v>0.009299999999999999</v>
       </c>
       <c r="I109" t="n">
-        <v>82.558853</v>
+        <v>8255.8853</v>
       </c>
     </row>
     <row r="110">
@@ -3995,7 +3995,7 @@
         <v>0.0083</v>
       </c>
       <c r="I110" t="n">
-        <v>83.244962</v>
+        <v>8324.4962</v>
       </c>
     </row>
     <row r="111">
@@ -4028,7 +4028,7 @@
         <v>0.0103</v>
       </c>
       <c r="I111" t="n">
-        <v>84.048225</v>
+        <v>8404.8225</v>
       </c>
     </row>
     <row r="112">
@@ -4061,7 +4061,7 @@
         <v>0.0102</v>
       </c>
       <c r="I112" t="n">
-        <v>83.742503</v>
+        <v>8374.2503</v>
       </c>
     </row>
     <row r="113">
@@ -4094,7 +4094,7 @@
         <v>0.0103</v>
       </c>
       <c r="I113" t="n">
-        <v>83.00784299999999</v>
+        <v>8300.784299999999</v>
       </c>
     </row>
     <row r="114">
@@ -4127,7 +4127,7 @@
         <v>0.0117</v>
       </c>
       <c r="I114" t="n">
-        <v>83.92501799999999</v>
+        <v>8392.5018</v>
       </c>
     </row>
     <row r="115">
@@ -4160,7 +4160,7 @@
         <v>0.0107</v>
       </c>
       <c r="I115" t="n">
-        <v>85.166286</v>
+        <v>8516.6286</v>
       </c>
     </row>
     <row r="116">
@@ -4193,7 +4193,7 @@
         <v>0.0102</v>
       </c>
       <c r="I116" t="n">
-        <v>86.215993</v>
+        <v>8621.5993</v>
       </c>
     </row>
     <row r="117">
@@ -4226,7 +4226,7 @@
         <v>0.0102</v>
       </c>
       <c r="I117" t="n">
-        <v>85.532411</v>
+        <v>8553.241099999999</v>
       </c>
     </row>
     <row r="118">
@@ -4259,7 +4259,7 @@
         <v>0.0112</v>
       </c>
       <c r="I118" t="n">
-        <v>85.36599200000001</v>
+        <v>8536.599200000001</v>
       </c>
     </row>
     <row r="119">
@@ -4292,7 +4292,7 @@
         <v>0.0112</v>
       </c>
       <c r="I119" t="n">
-        <v>85.365269</v>
+        <v>8536.526900000001</v>
       </c>
     </row>
     <row r="120">
@@ -4325,7 +4325,7 @@
         <v>0.0092</v>
       </c>
       <c r="I120" t="n">
-        <v>86.45939199999999</v>
+        <v>8645.939200000001</v>
       </c>
     </row>
     <row r="121">
@@ -4358,7 +4358,7 @@
         <v>0.0117</v>
       </c>
       <c r="I121" t="n">
-        <v>88.76237999999999</v>
+        <v>8876.237999999999</v>
       </c>
     </row>
     <row r="122">
@@ -4391,7 +4391,7 @@
         <v>0.0092</v>
       </c>
       <c r="I122" t="n">
-        <v>90.555673</v>
+        <v>9055.567300000001</v>
       </c>
     </row>
     <row r="123">
@@ -4424,7 +4424,7 @@
         <v>0.0112</v>
       </c>
       <c r="I123" t="n">
-        <v>91.966838</v>
+        <v>9196.683800000001</v>
       </c>
     </row>
     <row r="124">
@@ -5046,7 +5046,7 @@
         <v>0.0083</v>
       </c>
       <c r="I143" t="n">
-        <v>83.244962</v>
+        <v>8324.4962</v>
       </c>
     </row>
     <row r="144">
@@ -5079,7 +5079,7 @@
         <v>0.0103</v>
       </c>
       <c r="I144" t="n">
-        <v>84.048225</v>
+        <v>8404.8225</v>
       </c>
     </row>
     <row r="145">
@@ -5112,7 +5112,7 @@
         <v>0.0102</v>
       </c>
       <c r="I145" t="n">
-        <v>83.742503</v>
+        <v>8374.2503</v>
       </c>
     </row>
     <row r="146">
@@ -5145,7 +5145,7 @@
         <v>0.0103</v>
       </c>
       <c r="I146" t="n">
-        <v>83.00784299999999</v>
+        <v>8300.784299999999</v>
       </c>
     </row>
     <row r="147">
@@ -5178,7 +5178,7 @@
         <v>0.0117</v>
       </c>
       <c r="I147" t="n">
-        <v>83.92501799999999</v>
+        <v>8392.5018</v>
       </c>
     </row>
     <row r="148">
@@ -5211,7 +5211,7 @@
         <v>0.0102</v>
       </c>
       <c r="I148" t="n">
-        <v>86.215993</v>
+        <v>8621.5993</v>
       </c>
     </row>
     <row r="149">
@@ -5244,7 +5244,7 @@
         <v>0.0102</v>
       </c>
       <c r="I149" t="n">
-        <v>85.532411</v>
+        <v>8553.241099999999</v>
       </c>
     </row>
     <row r="150">
@@ -5277,7 +5277,7 @@
         <v>0.0112</v>
       </c>
       <c r="I150" t="n">
-        <v>85.36599200000001</v>
+        <v>8536.599200000001</v>
       </c>
     </row>
     <row r="151">
@@ -5310,7 +5310,7 @@
         <v>0.0112</v>
       </c>
       <c r="I151" t="n">
-        <v>85.365269</v>
+        <v>8536.526900000001</v>
       </c>
     </row>
     <row r="152">
@@ -5343,7 +5343,7 @@
         <v>0.0092</v>
       </c>
       <c r="I152" t="n">
-        <v>86.45939199999999</v>
+        <v>8645.939200000001</v>
       </c>
     </row>
     <row r="153">
@@ -5376,7 +5376,7 @@
         <v>0.0117</v>
       </c>
       <c r="I153" t="n">
-        <v>88.76237999999999</v>
+        <v>8876.237999999999</v>
       </c>
     </row>
     <row r="154">
@@ -5409,7 +5409,7 @@
         <v>0.0092</v>
       </c>
       <c r="I154" t="n">
-        <v>90.555673</v>
+        <v>9055.567300000001</v>
       </c>
     </row>
     <row r="155">
@@ -5442,7 +5442,7 @@
         <v>0.0112</v>
       </c>
       <c r="I155" t="n">
-        <v>91.966838</v>
+        <v>9196.683800000001</v>
       </c>
     </row>
     <row r="156">
@@ -6343,7 +6343,7 @@
         <v>0.0083</v>
       </c>
       <c r="I184" t="n">
-        <v>83.244962</v>
+        <v>8324.4962</v>
       </c>
     </row>
     <row r="185">
@@ -6376,7 +6376,7 @@
         <v>0.0103</v>
       </c>
       <c r="I185" t="n">
-        <v>84.048225</v>
+        <v>8404.8225</v>
       </c>
     </row>
     <row r="186">
@@ -6409,7 +6409,7 @@
         <v>0.0102</v>
       </c>
       <c r="I186" t="n">
-        <v>83.742503</v>
+        <v>8374.2503</v>
       </c>
     </row>
     <row r="187">
@@ -6442,7 +6442,7 @@
         <v>0.0103</v>
       </c>
       <c r="I187" t="n">
-        <v>83.00784299999999</v>
+        <v>8300.784299999999</v>
       </c>
     </row>
     <row r="188">
@@ -6475,7 +6475,7 @@
         <v>0.0117</v>
       </c>
       <c r="I188" t="n">
-        <v>83.92501799999999</v>
+        <v>8392.5018</v>
       </c>
     </row>
     <row r="189">
@@ -6508,7 +6508,7 @@
         <v>0.0107</v>
       </c>
       <c r="I189" t="n">
-        <v>85.166286</v>
+        <v>8516.6286</v>
       </c>
     </row>
     <row r="190">
@@ -6541,7 +6541,7 @@
         <v>0.0102</v>
       </c>
       <c r="I190" t="n">
-        <v>86.215993</v>
+        <v>8621.5993</v>
       </c>
     </row>
     <row r="191">
@@ -6574,7 +6574,7 @@
         <v>0.0102</v>
       </c>
       <c r="I191" t="n">
-        <v>85.532411</v>
+        <v>8553.241099999999</v>
       </c>
     </row>
     <row r="192">
@@ -6607,7 +6607,7 @@
         <v>0.0112</v>
       </c>
       <c r="I192" t="n">
-        <v>85.36599200000001</v>
+        <v>8536.599200000001</v>
       </c>
     </row>
     <row r="193">
@@ -6640,7 +6640,7 @@
         <v>0.0112</v>
       </c>
       <c r="I193" t="n">
-        <v>85.365269</v>
+        <v>8536.526900000001</v>
       </c>
     </row>
     <row r="194">
@@ -6673,7 +6673,7 @@
         <v>0.0092</v>
       </c>
       <c r="I194" t="n">
-        <v>86.45939199999999</v>
+        <v>8645.939200000001</v>
       </c>
     </row>
     <row r="195">
@@ -6706,7 +6706,7 @@
         <v>0.0117</v>
       </c>
       <c r="I195" t="n">
-        <v>88.76237999999999</v>
+        <v>8876.237999999999</v>
       </c>
     </row>
     <row r="196">
@@ -6739,7 +6739,7 @@
         <v>0.0092</v>
       </c>
       <c r="I196" t="n">
-        <v>90.555673</v>
+        <v>9055.567300000001</v>
       </c>
     </row>
     <row r="197">
@@ -6772,7 +6772,7 @@
         <v>0.0112</v>
       </c>
       <c r="I197" t="n">
-        <v>91.966838</v>
+        <v>9196.683800000001</v>
       </c>
     </row>
     <row r="198">
@@ -7363,7 +7363,7 @@
         <v>0.0083</v>
       </c>
       <c r="I216" t="n">
-        <v>83.244962</v>
+        <v>8324.4962</v>
       </c>
     </row>
     <row r="217">
@@ -7396,7 +7396,7 @@
         <v>0.0103</v>
       </c>
       <c r="I217" t="n">
-        <v>84.048225</v>
+        <v>8404.8225</v>
       </c>
     </row>
     <row r="218">
@@ -7429,7 +7429,7 @@
         <v>0.0102</v>
       </c>
       <c r="I218" t="n">
-        <v>83.742503</v>
+        <v>8374.2503</v>
       </c>
     </row>
     <row r="219">
@@ -7462,7 +7462,7 @@
         <v>0.0103</v>
       </c>
       <c r="I219" t="n">
-        <v>83.00784299999999</v>
+        <v>8300.784299999999</v>
       </c>
     </row>
     <row r="220">
@@ -7495,7 +7495,7 @@
         <v>0.0117</v>
       </c>
       <c r="I220" t="n">
-        <v>83.92501799999999</v>
+        <v>8392.5018</v>
       </c>
     </row>
     <row r="221">
@@ -7528,7 +7528,7 @@
         <v>0.0107</v>
       </c>
       <c r="I221" t="n">
-        <v>85.166286</v>
+        <v>8516.6286</v>
       </c>
     </row>
     <row r="222">
@@ -7561,7 +7561,7 @@
         <v>0.0102</v>
       </c>
       <c r="I222" t="n">
-        <v>86.215993</v>
+        <v>8621.5993</v>
       </c>
     </row>
     <row r="223">
@@ -7594,7 +7594,7 @@
         <v>0.0102</v>
       </c>
       <c r="I223" t="n">
-        <v>85.532411</v>
+        <v>8553.241099999999</v>
       </c>
     </row>
     <row r="224">
@@ -7627,7 +7627,7 @@
         <v>0.0112</v>
       </c>
       <c r="I224" t="n">
-        <v>85.36599200000001</v>
+        <v>8536.599200000001</v>
       </c>
     </row>
     <row r="225">
@@ -7660,7 +7660,7 @@
         <v>0.0112</v>
       </c>
       <c r="I225" t="n">
-        <v>85.365269</v>
+        <v>8536.526900000001</v>
       </c>
     </row>
     <row r="226">
@@ -7693,7 +7693,7 @@
         <v>0.0092</v>
       </c>
       <c r="I226" t="n">
-        <v>86.45939199999999</v>
+        <v>8645.939200000001</v>
       </c>
     </row>
     <row r="227">
@@ -7726,7 +7726,7 @@
         <v>0.0117</v>
       </c>
       <c r="I227" t="n">
-        <v>88.76237999999999</v>
+        <v>8876.237999999999</v>
       </c>
     </row>
     <row r="228">
@@ -7759,7 +7759,7 @@
         <v>0.0092</v>
       </c>
       <c r="I228" t="n">
-        <v>90.555673</v>
+        <v>9055.567300000001</v>
       </c>
     </row>
     <row r="229">
@@ -7792,7 +7792,7 @@
         <v>0.0112</v>
       </c>
       <c r="I229" t="n">
-        <v>91.966838</v>
+        <v>9196.683800000001</v>
       </c>
     </row>
     <row r="230">
@@ -8414,7 +8414,7 @@
         <v>0.0083</v>
       </c>
       <c r="I249" t="n">
-        <v>83.244962</v>
+        <v>8324.4962</v>
       </c>
     </row>
     <row r="250">
@@ -8447,7 +8447,7 @@
         <v>0.0103</v>
       </c>
       <c r="I250" t="n">
-        <v>84.048225</v>
+        <v>8404.8225</v>
       </c>
     </row>
     <row r="251">
@@ -8480,7 +8480,7 @@
         <v>0.0102</v>
       </c>
       <c r="I251" t="n">
-        <v>83.742503</v>
+        <v>8374.2503</v>
       </c>
     </row>
     <row r="252">
@@ -8513,7 +8513,7 @@
         <v>0.0103</v>
       </c>
       <c r="I252" t="n">
-        <v>83.00784299999999</v>
+        <v>8300.784299999999</v>
       </c>
     </row>
     <row r="253">
@@ -8546,7 +8546,7 @@
         <v>0.0117</v>
       </c>
       <c r="I253" t="n">
-        <v>83.92501799999999</v>
+        <v>8392.5018</v>
       </c>
     </row>
     <row r="254">
@@ -8579,7 +8579,7 @@
         <v>0.0107</v>
       </c>
       <c r="I254" t="n">
-        <v>85.166286</v>
+        <v>8516.6286</v>
       </c>
     </row>
     <row r="255">
@@ -8612,7 +8612,7 @@
         <v>0.0102</v>
       </c>
       <c r="I255" t="n">
-        <v>86.215993</v>
+        <v>8621.5993</v>
       </c>
     </row>
     <row r="256">
@@ -8645,7 +8645,7 @@
         <v>0.0102</v>
       </c>
       <c r="I256" t="n">
-        <v>85.532411</v>
+        <v>8553.241099999999</v>
       </c>
     </row>
     <row r="257">
@@ -8678,7 +8678,7 @@
         <v>0.0112</v>
       </c>
       <c r="I257" t="n">
-        <v>85.36599200000001</v>
+        <v>8536.599200000001</v>
       </c>
     </row>
     <row r="258">
@@ -8711,7 +8711,7 @@
         <v>0.0112</v>
       </c>
       <c r="I258" t="n">
-        <v>85.365269</v>
+        <v>8536.526900000001</v>
       </c>
     </row>
     <row r="259">
@@ -8744,7 +8744,7 @@
         <v>0.0092</v>
       </c>
       <c r="I259" t="n">
-        <v>86.45939199999999</v>
+        <v>8645.939200000001</v>
       </c>
     </row>
     <row r="260">
@@ -8777,7 +8777,7 @@
         <v>0.0117</v>
       </c>
       <c r="I260" t="n">
-        <v>88.76237999999999</v>
+        <v>8876.237999999999</v>
       </c>
     </row>
     <row r="261">
@@ -8810,7 +8810,7 @@
         <v>0.0092</v>
       </c>
       <c r="I261" t="n">
-        <v>90.555673</v>
+        <v>9055.567300000001</v>
       </c>
     </row>
     <row r="262">
@@ -8843,7 +8843,7 @@
         <v>0.0112</v>
       </c>
       <c r="I262" t="n">
-        <v>91.966838</v>
+        <v>9196.683800000001</v>
       </c>
     </row>
     <row r="263">
@@ -9465,7 +9465,7 @@
         <v>0.0083</v>
       </c>
       <c r="I282" t="n">
-        <v>83.244962</v>
+        <v>8324.4962</v>
       </c>
     </row>
     <row r="283">
@@ -9498,7 +9498,7 @@
         <v>0.0103</v>
       </c>
       <c r="I283" t="n">
-        <v>84.048225</v>
+        <v>8404.8225</v>
       </c>
     </row>
     <row r="284">
@@ -9531,7 +9531,7 @@
         <v>0.0102</v>
       </c>
       <c r="I284" t="n">
-        <v>83.742503</v>
+        <v>8374.2503</v>
       </c>
     </row>
     <row r="285">
@@ -9564,7 +9564,7 @@
         <v>0.0103</v>
       </c>
       <c r="I285" t="n">
-        <v>83.00784299999999</v>
+        <v>8300.784299999999</v>
       </c>
     </row>
     <row r="286">
@@ -9597,7 +9597,7 @@
         <v>0.0117</v>
       </c>
       <c r="I286" t="n">
-        <v>83.92501799999999</v>
+        <v>8392.5018</v>
       </c>
     </row>
     <row r="287">
@@ -9630,7 +9630,7 @@
         <v>0.0107</v>
       </c>
       <c r="I287" t="n">
-        <v>85.166286</v>
+        <v>8516.6286</v>
       </c>
     </row>
     <row r="288">
@@ -9663,7 +9663,7 @@
         <v>0.0102</v>
       </c>
       <c r="I288" t="n">
-        <v>86.215993</v>
+        <v>8621.5993</v>
       </c>
     </row>
     <row r="289">
@@ -9696,7 +9696,7 @@
         <v>0.0102</v>
       </c>
       <c r="I289" t="n">
-        <v>85.532411</v>
+        <v>8553.241099999999</v>
       </c>
     </row>
     <row r="290">
@@ -9729,7 +9729,7 @@
         <v>0.0112</v>
       </c>
       <c r="I290" t="n">
-        <v>85.36599200000001</v>
+        <v>8536.599200000001</v>
       </c>
     </row>
     <row r="291">
@@ -9762,7 +9762,7 @@
         <v>0.0112</v>
       </c>
       <c r="I291" t="n">
-        <v>85.365269</v>
+        <v>8536.526900000001</v>
       </c>
     </row>
     <row r="292">
@@ -9795,7 +9795,7 @@
         <v>0.0092</v>
       </c>
       <c r="I292" t="n">
-        <v>86.45939199999999</v>
+        <v>8645.939200000001</v>
       </c>
     </row>
     <row r="293">
@@ -9828,7 +9828,7 @@
         <v>0.0117</v>
       </c>
       <c r="I293" t="n">
-        <v>88.76237999999999</v>
+        <v>8876.237999999999</v>
       </c>
     </row>
     <row r="294">
@@ -9861,7 +9861,7 @@
         <v>0.0092</v>
       </c>
       <c r="I294" t="n">
-        <v>90.555673</v>
+        <v>9055.567300000001</v>
       </c>
     </row>
     <row r="295">
@@ -9894,7 +9894,7 @@
         <v>0.0112</v>
       </c>
       <c r="I295" t="n">
-        <v>91.966838</v>
+        <v>9196.683800000001</v>
       </c>
     </row>
     <row r="296">
@@ -10516,7 +10516,7 @@
         <v>0.0083</v>
       </c>
       <c r="I315" t="n">
-        <v>83.244962</v>
+        <v>8324.4962</v>
       </c>
     </row>
     <row r="316">
@@ -10549,7 +10549,7 @@
         <v>0.0103</v>
       </c>
       <c r="I316" t="n">
-        <v>84.048225</v>
+        <v>8404.8225</v>
       </c>
     </row>
     <row r="317">
@@ -10582,7 +10582,7 @@
         <v>0.0102</v>
       </c>
       <c r="I317" t="n">
-        <v>83.742503</v>
+        <v>8374.2503</v>
       </c>
     </row>
     <row r="318">
@@ -10615,7 +10615,7 @@
         <v>0.0103</v>
       </c>
       <c r="I318" t="n">
-        <v>83.00784299999999</v>
+        <v>8300.784299999999</v>
       </c>
     </row>
     <row r="319">
@@ -10648,7 +10648,7 @@
         <v>0.0117</v>
       </c>
       <c r="I319" t="n">
-        <v>83.92501799999999</v>
+        <v>8392.5018</v>
       </c>
     </row>
     <row r="320">
@@ -10681,7 +10681,7 @@
         <v>0.0107</v>
       </c>
       <c r="I320" t="n">
-        <v>85.166286</v>
+        <v>8516.6286</v>
       </c>
     </row>
     <row r="321">
@@ -10714,7 +10714,7 @@
         <v>0.0102</v>
       </c>
       <c r="I321" t="n">
-        <v>86.215993</v>
+        <v>8621.5993</v>
       </c>
     </row>
     <row r="322">
@@ -10747,7 +10747,7 @@
         <v>0.0102</v>
       </c>
       <c r="I322" t="n">
-        <v>85.532411</v>
+        <v>8553.241099999999</v>
       </c>
     </row>
     <row r="323">
@@ -10780,7 +10780,7 @@
         <v>0.0112</v>
       </c>
       <c r="I323" t="n">
-        <v>85.36599200000001</v>
+        <v>8536.599200000001</v>
       </c>
     </row>
     <row r="324">
@@ -10813,7 +10813,7 @@
         <v>0.0112</v>
       </c>
       <c r="I324" t="n">
-        <v>85.365269</v>
+        <v>8536.526900000001</v>
       </c>
     </row>
     <row r="325">
@@ -10846,7 +10846,7 @@
         <v>0.0092</v>
       </c>
       <c r="I325" t="n">
-        <v>86.45939199999999</v>
+        <v>8645.939200000001</v>
       </c>
     </row>
     <row r="326">
@@ -10879,7 +10879,7 @@
         <v>0.0117</v>
       </c>
       <c r="I326" t="n">
-        <v>88.76237999999999</v>
+        <v>8876.237999999999</v>
       </c>
     </row>
     <row r="327">
@@ -10912,7 +10912,7 @@
         <v>0.0092</v>
       </c>
       <c r="I327" t="n">
-        <v>90.555673</v>
+        <v>9055.567300000001</v>
       </c>
     </row>
     <row r="328">
@@ -10945,7 +10945,7 @@
         <v>0.0112</v>
       </c>
       <c r="I328" t="n">
-        <v>91.966838</v>
+        <v>9196.683800000001</v>
       </c>
     </row>
     <row r="329">
@@ -11567,7 +11567,7 @@
         <v>0.0083</v>
       </c>
       <c r="I348" t="n">
-        <v>83.244962</v>
+        <v>8324.4962</v>
       </c>
     </row>
     <row r="349">
@@ -11600,7 +11600,7 @@
         <v>0.0103</v>
       </c>
       <c r="I349" t="n">
-        <v>84.048225</v>
+        <v>8404.8225</v>
       </c>
     </row>
     <row r="350">
@@ -11633,7 +11633,7 @@
         <v>0.0102</v>
       </c>
       <c r="I350" t="n">
-        <v>83.742503</v>
+        <v>8374.2503</v>
       </c>
     </row>
     <row r="351">
@@ -11666,7 +11666,7 @@
         <v>0.0103</v>
       </c>
       <c r="I351" t="n">
-        <v>83.00784299999999</v>
+        <v>8300.784299999999</v>
       </c>
     </row>
     <row r="352">
@@ -11699,7 +11699,7 @@
         <v>0.0117</v>
       </c>
       <c r="I352" t="n">
-        <v>83.92501799999999</v>
+        <v>8392.5018</v>
       </c>
     </row>
     <row r="353">
@@ -11732,7 +11732,7 @@
         <v>0.0107</v>
       </c>
       <c r="I353" t="n">
-        <v>85.166286</v>
+        <v>8516.6286</v>
       </c>
     </row>
     <row r="354">
@@ -11765,7 +11765,7 @@
         <v>0.0102</v>
       </c>
       <c r="I354" t="n">
-        <v>86.215993</v>
+        <v>8621.5993</v>
       </c>
     </row>
     <row r="355">
@@ -11798,7 +11798,7 @@
         <v>0.0102</v>
       </c>
       <c r="I355" t="n">
-        <v>85.532411</v>
+        <v>8553.241099999999</v>
       </c>
     </row>
     <row r="356">
@@ -11831,7 +11831,7 @@
         <v>0.0112</v>
       </c>
       <c r="I356" t="n">
-        <v>85.36599200000001</v>
+        <v>8536.599200000001</v>
       </c>
     </row>
     <row r="357">
@@ -11864,7 +11864,7 @@
         <v>0.0112</v>
       </c>
       <c r="I357" t="n">
-        <v>85.365269</v>
+        <v>8536.526900000001</v>
       </c>
     </row>
     <row r="358">
@@ -11897,7 +11897,7 @@
         <v>0.0092</v>
       </c>
       <c r="I358" t="n">
-        <v>86.45939199999999</v>
+        <v>8645.939200000001</v>
       </c>
     </row>
     <row r="359">
@@ -11930,7 +11930,7 @@
         <v>0.0117</v>
       </c>
       <c r="I359" t="n">
-        <v>88.76237999999999</v>
+        <v>8876.237999999999</v>
       </c>
     </row>
     <row r="360">
@@ -11963,7 +11963,7 @@
         <v>0.0092</v>
       </c>
       <c r="I360" t="n">
-        <v>90.555673</v>
+        <v>9055.567300000001</v>
       </c>
     </row>
     <row r="361">
@@ -11996,7 +11996,7 @@
         <v>0.0112</v>
       </c>
       <c r="I361" t="n">
-        <v>91.966838</v>
+        <v>9196.683800000001</v>
       </c>
     </row>
     <row r="362">
@@ -12618,7 +12618,7 @@
         <v>0.0083</v>
       </c>
       <c r="I381" t="n">
-        <v>83.244962</v>
+        <v>8324.4962</v>
       </c>
     </row>
     <row r="382">
@@ -12651,7 +12651,7 @@
         <v>0.0103</v>
       </c>
       <c r="I382" t="n">
-        <v>84.048225</v>
+        <v>8404.8225</v>
       </c>
     </row>
     <row r="383">
@@ -12684,7 +12684,7 @@
         <v>0.0102</v>
       </c>
       <c r="I383" t="n">
-        <v>83.742503</v>
+        <v>8374.2503</v>
       </c>
     </row>
     <row r="384">
@@ -12717,7 +12717,7 @@
         <v>0.0103</v>
       </c>
       <c r="I384" t="n">
-        <v>83.00784299999999</v>
+        <v>8300.784299999999</v>
       </c>
     </row>
     <row r="385">
@@ -12750,7 +12750,7 @@
         <v>0.0117</v>
       </c>
       <c r="I385" t="n">
-        <v>83.92501799999999</v>
+        <v>8392.5018</v>
       </c>
     </row>
     <row r="386">
@@ -12783,7 +12783,7 @@
         <v>0.0107</v>
       </c>
       <c r="I386" t="n">
-        <v>85.166286</v>
+        <v>8516.6286</v>
       </c>
     </row>
     <row r="387">
@@ -12816,7 +12816,7 @@
         <v>0.0102</v>
       </c>
       <c r="I387" t="n">
-        <v>86.215993</v>
+        <v>8621.5993</v>
       </c>
     </row>
     <row r="388">
@@ -12849,7 +12849,7 @@
         <v>0.0102</v>
       </c>
       <c r="I388" t="n">
-        <v>85.532411</v>
+        <v>8553.241099999999</v>
       </c>
     </row>
     <row r="389">
@@ -12882,7 +12882,7 @@
         <v>0.0112</v>
       </c>
       <c r="I389" t="n">
-        <v>85.36599200000001</v>
+        <v>8536.599200000001</v>
       </c>
     </row>
     <row r="390">
@@ -12915,7 +12915,7 @@
         <v>0.0112</v>
       </c>
       <c r="I390" t="n">
-        <v>85.365269</v>
+        <v>8536.526900000001</v>
       </c>
     </row>
     <row r="391">
@@ -12948,7 +12948,7 @@
         <v>0.0092</v>
       </c>
       <c r="I391" t="n">
-        <v>86.45939199999999</v>
+        <v>8645.939200000001</v>
       </c>
     </row>
     <row r="392">
@@ -12981,7 +12981,7 @@
         <v>0.0117</v>
       </c>
       <c r="I392" t="n">
-        <v>88.76237999999999</v>
+        <v>8876.237999999999</v>
       </c>
     </row>
     <row r="393">
@@ -13014,7 +13014,7 @@
         <v>0.0092</v>
       </c>
       <c r="I393" t="n">
-        <v>90.555673</v>
+        <v>9055.567300000001</v>
       </c>
     </row>
     <row r="394">
@@ -13047,7 +13047,7 @@
         <v>0.0112</v>
       </c>
       <c r="I394" t="n">
-        <v>91.966838</v>
+        <v>9196.683800000001</v>
       </c>
     </row>
     <row r="395">
@@ -13669,7 +13669,7 @@
         <v>0.0013</v>
       </c>
       <c r="I414" t="n">
-        <v>79.36756</v>
+        <v>7936.756</v>
       </c>
     </row>
     <row r="415">
@@ -13702,7 +13702,7 @@
         <v>0.002</v>
       </c>
       <c r="I415" t="n">
-        <v>79.00167500000001</v>
+        <v>7900.1675</v>
       </c>
     </row>
     <row r="416">
@@ -13735,7 +13735,7 @@
         <v>0.0021</v>
       </c>
       <c r="I416" t="n">
-        <v>79.516036</v>
+        <v>7951.6036</v>
       </c>
     </row>
     <row r="417">
@@ -13768,7 +13768,7 @@
         <v>0.0027</v>
       </c>
       <c r="I417" t="n">
-        <v>80.357348</v>
+        <v>8035.7348</v>
       </c>
     </row>
     <row r="418">
@@ -13801,7 +13801,7 @@
         <v>0.0031</v>
       </c>
       <c r="I418" t="n">
-        <v>80.695116</v>
+        <v>8069.5116</v>
       </c>
     </row>
     <row r="419">
@@ -13834,7 +13834,7 @@
         <v>0.0036</v>
       </c>
       <c r="I419" t="n">
-        <v>80.393818</v>
+        <v>8039.3818</v>
       </c>
     </row>
     <row r="420">
@@ -13867,7 +13867,7 @@
         <v>0.0043</v>
       </c>
       <c r="I420" t="n">
-        <v>79.517839</v>
+        <v>7951.7839</v>
       </c>
     </row>
     <row r="421">
@@ -13900,7 +13900,7 @@
         <v>0.0044</v>
       </c>
       <c r="I421" t="n">
-        <v>79.412036</v>
+        <v>7941.2036</v>
       </c>
     </row>
     <row r="422">
@@ -13933,7 +13933,7 @@
         <v>0.0049</v>
       </c>
       <c r="I422" t="n">
-        <v>77.391648</v>
+        <v>7739.1648</v>
       </c>
     </row>
     <row r="423">
@@ -13966,7 +13966,7 @@
         <v>0.0059</v>
       </c>
       <c r="I423" t="n">
-        <v>80.074422</v>
+        <v>8007.4422</v>
       </c>
     </row>
     <row r="424">
@@ -13999,7 +13999,7 @@
         <v>0.0077</v>
       </c>
       <c r="I424" t="n">
-        <v>80.216174</v>
+        <v>8021.6174</v>
       </c>
     </row>
     <row r="425">
@@ -14032,7 +14032,7 @@
         <v>0.0073</v>
       </c>
       <c r="I425" t="n">
-        <v>79.665268</v>
+        <v>7966.5268</v>
       </c>
     </row>
     <row r="426">
@@ -14065,7 +14065,7 @@
         <v>0.0076</v>
       </c>
       <c r="I426" t="n">
-        <v>80.099069</v>
+        <v>8009.9069</v>
       </c>
     </row>
     <row r="427">
@@ -14098,7 +14098,7 @@
         <v>0.009299999999999999</v>
       </c>
       <c r="I427" t="n">
-        <v>82.558853</v>
+        <v>8255.8853</v>
       </c>
     </row>
     <row r="428">
@@ -14131,7 +14131,7 @@
         <v>0.0083</v>
       </c>
       <c r="I428" t="n">
-        <v>83.244962</v>
+        <v>8324.4962</v>
       </c>
     </row>
     <row r="429">
@@ -14164,7 +14164,7 @@
         <v>0.0103</v>
       </c>
       <c r="I429" t="n">
-        <v>84.048225</v>
+        <v>8404.8225</v>
       </c>
     </row>
     <row r="430">
@@ -14197,7 +14197,7 @@
         <v>0.0102</v>
       </c>
       <c r="I430" t="n">
-        <v>83.742503</v>
+        <v>8374.2503</v>
       </c>
     </row>
     <row r="431">
@@ -14230,7 +14230,7 @@
         <v>0.0103</v>
       </c>
       <c r="I431" t="n">
-        <v>83.00784299999999</v>
+        <v>8300.784299999999</v>
       </c>
     </row>
     <row r="432">
@@ -14263,7 +14263,7 @@
         <v>0.0117</v>
       </c>
       <c r="I432" t="n">
-        <v>83.92501799999999</v>
+        <v>8392.5018</v>
       </c>
     </row>
     <row r="433">
@@ -14296,7 +14296,7 @@
         <v>0.0107</v>
       </c>
       <c r="I433" t="n">
-        <v>85.166286</v>
+        <v>8516.6286</v>
       </c>
     </row>
     <row r="434">
@@ -14329,7 +14329,7 @@
         <v>0.0102</v>
       </c>
       <c r="I434" t="n">
-        <v>86.215993</v>
+        <v>8621.5993</v>
       </c>
     </row>
     <row r="435">
@@ -14362,7 +14362,7 @@
         <v>0.0102</v>
       </c>
       <c r="I435" t="n">
-        <v>85.532411</v>
+        <v>8553.241099999999</v>
       </c>
     </row>
     <row r="436">
@@ -14395,7 +14395,7 @@
         <v>0.0112</v>
       </c>
       <c r="I436" t="n">
-        <v>85.36599200000001</v>
+        <v>8536.599200000001</v>
       </c>
     </row>
     <row r="437">
@@ -14428,7 +14428,7 @@
         <v>0.0112</v>
       </c>
       <c r="I437" t="n">
-        <v>85.365269</v>
+        <v>8536.526900000001</v>
       </c>
     </row>
     <row r="438">
@@ -14461,7 +14461,7 @@
         <v>0.0092</v>
       </c>
       <c r="I438" t="n">
-        <v>86.45939199999999</v>
+        <v>8645.939200000001</v>
       </c>
     </row>
     <row r="439">
@@ -14494,7 +14494,7 @@
         <v>0.0117</v>
       </c>
       <c r="I439" t="n">
-        <v>88.76237999999999</v>
+        <v>8876.237999999999</v>
       </c>
     </row>
     <row r="440">
@@ -14527,7 +14527,7 @@
         <v>0.0092</v>
       </c>
       <c r="I440" t="n">
-        <v>90.555673</v>
+        <v>9055.567300000001</v>
       </c>
     </row>
     <row r="441">
@@ -14560,7 +14560,7 @@
         <v>0.0112</v>
       </c>
       <c r="I441" t="n">
-        <v>91.966838</v>
+        <v>9196.683800000001</v>
       </c>
     </row>
     <row r="442">
@@ -15151,7 +15151,7 @@
         <v>0.0083</v>
       </c>
       <c r="I460" t="n">
-        <v>83.244962</v>
+        <v>8324.4962</v>
       </c>
     </row>
     <row r="461">
@@ -15184,7 +15184,7 @@
         <v>0.0103</v>
       </c>
       <c r="I461" t="n">
-        <v>84.048225</v>
+        <v>8404.8225</v>
       </c>
     </row>
     <row r="462">
@@ -15217,7 +15217,7 @@
         <v>0.0102</v>
       </c>
       <c r="I462" t="n">
-        <v>83.742503</v>
+        <v>8374.2503</v>
       </c>
     </row>
     <row r="463">
@@ -15250,7 +15250,7 @@
         <v>0.0103</v>
       </c>
       <c r="I463" t="n">
-        <v>83.00784299999999</v>
+        <v>8300.784299999999</v>
       </c>
     </row>
     <row r="464">
@@ -15283,7 +15283,7 @@
         <v>0.0117</v>
       </c>
       <c r="I464" t="n">
-        <v>83.92501799999999</v>
+        <v>8392.5018</v>
       </c>
     </row>
     <row r="465">
@@ -15316,7 +15316,7 @@
         <v>0.0107</v>
       </c>
       <c r="I465" t="n">
-        <v>85.166286</v>
+        <v>8516.6286</v>
       </c>
     </row>
     <row r="466">
@@ -15349,7 +15349,7 @@
         <v>0.0102</v>
       </c>
       <c r="I466" t="n">
-        <v>86.215993</v>
+        <v>8621.5993</v>
       </c>
     </row>
     <row r="467">
@@ -15382,7 +15382,7 @@
         <v>0.0102</v>
       </c>
       <c r="I467" t="n">
-        <v>85.532411</v>
+        <v>8553.241099999999</v>
       </c>
     </row>
     <row r="468">
@@ -15415,7 +15415,7 @@
         <v>0.0112</v>
       </c>
       <c r="I468" t="n">
-        <v>85.36599200000001</v>
+        <v>8536.599200000001</v>
       </c>
     </row>
     <row r="469">
@@ -15448,7 +15448,7 @@
         <v>0.0112</v>
       </c>
       <c r="I469" t="n">
-        <v>85.365269</v>
+        <v>8536.526900000001</v>
       </c>
     </row>
     <row r="470">
@@ -15481,7 +15481,7 @@
         <v>0.0092</v>
       </c>
       <c r="I470" t="n">
-        <v>86.45939199999999</v>
+        <v>8645.939200000001</v>
       </c>
     </row>
     <row r="471">
@@ -15514,7 +15514,7 @@
         <v>0.0117</v>
       </c>
       <c r="I471" t="n">
-        <v>88.76237999999999</v>
+        <v>8876.237999999999</v>
       </c>
     </row>
     <row r="472">
@@ -15547,7 +15547,7 @@
         <v>0.0092</v>
       </c>
       <c r="I472" t="n">
-        <v>90.555673</v>
+        <v>9055.567300000001</v>
       </c>
     </row>
     <row r="473">
@@ -15580,7 +15580,7 @@
         <v>0.0112</v>
       </c>
       <c r="I473" t="n">
-        <v>91.966838</v>
+        <v>9196.683800000001</v>
       </c>
     </row>
     <row r="474">
@@ -16202,7 +16202,7 @@
         <v>0.0103</v>
       </c>
       <c r="I493" t="n">
-        <v>84.048225</v>
+        <v>8404.8225</v>
       </c>
     </row>
     <row r="494">
@@ -16235,7 +16235,7 @@
         <v>0.0102</v>
       </c>
       <c r="I494" t="n">
-        <v>83.742503</v>
+        <v>8374.2503</v>
       </c>
     </row>
     <row r="495">
@@ -16268,7 +16268,7 @@
         <v>0.0103</v>
       </c>
       <c r="I495" t="n">
-        <v>83.00784299999999</v>
+        <v>8300.784299999999</v>
       </c>
     </row>
     <row r="496">
@@ -16301,7 +16301,7 @@
         <v>0.0117</v>
       </c>
       <c r="I496" t="n">
-        <v>83.92501799999999</v>
+        <v>8392.5018</v>
       </c>
     </row>
     <row r="497">
@@ -16334,7 +16334,7 @@
         <v>0.0107</v>
       </c>
       <c r="I497" t="n">
-        <v>85.166286</v>
+        <v>8516.6286</v>
       </c>
     </row>
     <row r="498">
@@ -16367,7 +16367,7 @@
         <v>0.0102</v>
       </c>
       <c r="I498" t="n">
-        <v>86.215993</v>
+        <v>8621.5993</v>
       </c>
     </row>
     <row r="499">
@@ -16400,7 +16400,7 @@
         <v>0.0102</v>
       </c>
       <c r="I499" t="n">
-        <v>85.532411</v>
+        <v>8553.241099999999</v>
       </c>
     </row>
     <row r="500">
@@ -16433,7 +16433,7 @@
         <v>0.0112</v>
       </c>
       <c r="I500" t="n">
-        <v>85.36599200000001</v>
+        <v>8536.599200000001</v>
       </c>
     </row>
     <row r="501">
@@ -16466,7 +16466,7 @@
         <v>0.0112</v>
       </c>
       <c r="I501" t="n">
-        <v>85.365269</v>
+        <v>8536.526900000001</v>
       </c>
     </row>
     <row r="502">
@@ -16499,7 +16499,7 @@
         <v>0.0092</v>
       </c>
       <c r="I502" t="n">
-        <v>86.45939199999999</v>
+        <v>8645.939200000001</v>
       </c>
     </row>
     <row r="503">
@@ -16532,7 +16532,7 @@
         <v>0.0117</v>
       </c>
       <c r="I503" t="n">
-        <v>88.76237999999999</v>
+        <v>8876.237999999999</v>
       </c>
     </row>
     <row r="504">
@@ -16565,7 +16565,7 @@
         <v>0.0092</v>
       </c>
       <c r="I504" t="n">
-        <v>90.555673</v>
+        <v>9055.567300000001</v>
       </c>
     </row>
     <row r="505">
@@ -16598,7 +16598,7 @@
         <v>0.0112</v>
       </c>
       <c r="I505" t="n">
-        <v>91.966838</v>
+        <v>9196.683800000001</v>
       </c>
     </row>
     <row r="506">
@@ -17220,7 +17220,7 @@
         <v>0.0083</v>
       </c>
       <c r="I525" t="n">
-        <v>83.244962</v>
+        <v>8324.4962</v>
       </c>
     </row>
     <row r="526">
@@ -17253,7 +17253,7 @@
         <v>0.0103</v>
       </c>
       <c r="I526" t="n">
-        <v>84.048225</v>
+        <v>8404.8225</v>
       </c>
     </row>
     <row r="527">
@@ -17286,7 +17286,7 @@
         <v>0.0102</v>
       </c>
       <c r="I527" t="n">
-        <v>83.742503</v>
+        <v>8374.2503</v>
       </c>
     </row>
     <row r="528">
@@ -17319,7 +17319,7 @@
         <v>0.0103</v>
       </c>
       <c r="I528" t="n">
-        <v>83.00784299999999</v>
+        <v>8300.784299999999</v>
       </c>
     </row>
     <row r="529">
@@ -17352,7 +17352,7 @@
         <v>0.0117</v>
       </c>
       <c r="I529" t="n">
-        <v>83.92501799999999</v>
+        <v>8392.5018</v>
       </c>
     </row>
     <row r="530">
@@ -17385,7 +17385,7 @@
         <v>0.0107</v>
       </c>
       <c r="I530" t="n">
-        <v>85.166286</v>
+        <v>8516.6286</v>
       </c>
     </row>
     <row r="531">
@@ -17418,7 +17418,7 @@
         <v>0.0102</v>
       </c>
       <c r="I531" t="n">
-        <v>86.215993</v>
+        <v>8621.5993</v>
       </c>
     </row>
     <row r="532">
@@ -17451,7 +17451,7 @@
         <v>0.0102</v>
       </c>
       <c r="I532" t="n">
-        <v>85.532411</v>
+        <v>8553.241099999999</v>
       </c>
     </row>
     <row r="533">
@@ -17484,7 +17484,7 @@
         <v>0.0112</v>
       </c>
       <c r="I533" t="n">
-        <v>85.36599200000001</v>
+        <v>8536.599200000001</v>
       </c>
     </row>
     <row r="534">
@@ -17517,7 +17517,7 @@
         <v>0.0112</v>
       </c>
       <c r="I534" t="n">
-        <v>85.365269</v>
+        <v>8536.526900000001</v>
       </c>
     </row>
     <row r="535">
@@ -17550,7 +17550,7 @@
         <v>0.0092</v>
       </c>
       <c r="I535" t="n">
-        <v>86.45939199999999</v>
+        <v>8645.939200000001</v>
       </c>
     </row>
     <row r="536">
@@ -17583,7 +17583,7 @@
         <v>0.0117</v>
       </c>
       <c r="I536" t="n">
-        <v>88.76237999999999</v>
+        <v>8876.237999999999</v>
       </c>
     </row>
     <row r="537">
@@ -17616,7 +17616,7 @@
         <v>0.0092</v>
       </c>
       <c r="I537" t="n">
-        <v>90.555673</v>
+        <v>9055.567300000001</v>
       </c>
     </row>
     <row r="538">
@@ -17649,7 +17649,7 @@
         <v>0.0112</v>
       </c>
       <c r="I538" t="n">
-        <v>91.966838</v>
+        <v>9196.683800000001</v>
       </c>
     </row>
     <row r="539">
@@ -18240,7 +18240,7 @@
         <v>0.0083</v>
       </c>
       <c r="I557" t="n">
-        <v>83.244962</v>
+        <v>8324.4962</v>
       </c>
     </row>
     <row r="558">
@@ -18273,7 +18273,7 @@
         <v>0.0103</v>
       </c>
       <c r="I558" t="n">
-        <v>84.048225</v>
+        <v>8404.8225</v>
       </c>
     </row>
     <row r="559">
@@ -18306,7 +18306,7 @@
         <v>0.0102</v>
       </c>
       <c r="I559" t="n">
-        <v>83.742503</v>
+        <v>8374.2503</v>
       </c>
     </row>
     <row r="560">
@@ -18339,7 +18339,7 @@
         <v>0.0103</v>
       </c>
       <c r="I560" t="n">
-        <v>83.00784299999999</v>
+        <v>8300.784299999999</v>
       </c>
     </row>
     <row r="561">
@@ -18372,7 +18372,7 @@
         <v>0.0117</v>
       </c>
       <c r="I561" t="n">
-        <v>83.92501799999999</v>
+        <v>8392.5018</v>
       </c>
     </row>
     <row r="562">
@@ -18405,7 +18405,7 @@
         <v>0.0107</v>
       </c>
       <c r="I562" t="n">
-        <v>85.166286</v>
+        <v>8516.6286</v>
       </c>
     </row>
     <row r="563">
@@ -18438,7 +18438,7 @@
         <v>0.0102</v>
       </c>
       <c r="I563" t="n">
-        <v>86.215993</v>
+        <v>8621.5993</v>
       </c>
     </row>
     <row r="564">
@@ -18471,7 +18471,7 @@
         <v>0.0102</v>
       </c>
       <c r="I564" t="n">
-        <v>85.532411</v>
+        <v>8553.241099999999</v>
       </c>
     </row>
     <row r="565">
@@ -18504,7 +18504,7 @@
         <v>0.0112</v>
       </c>
       <c r="I565" t="n">
-        <v>85.36599200000001</v>
+        <v>8536.599200000001</v>
       </c>
     </row>
     <row r="566">
@@ -18537,7 +18537,7 @@
         <v>0.0112</v>
       </c>
       <c r="I566" t="n">
-        <v>85.365269</v>
+        <v>8536.526900000001</v>
       </c>
     </row>
     <row r="567">
@@ -18570,7 +18570,7 @@
         <v>0.0092</v>
       </c>
       <c r="I567" t="n">
-        <v>86.45939199999999</v>
+        <v>8645.939200000001</v>
       </c>
     </row>
     <row r="568">
@@ -18603,7 +18603,7 @@
         <v>0.0117</v>
       </c>
       <c r="I568" t="n">
-        <v>88.76237999999999</v>
+        <v>8876.237999999999</v>
       </c>
     </row>
     <row r="569">
@@ -18636,7 +18636,7 @@
         <v>0.0092</v>
       </c>
       <c r="I569" t="n">
-        <v>90.555673</v>
+        <v>9055.567300000001</v>
       </c>
     </row>
     <row r="570">
@@ -18669,7 +18669,7 @@
         <v>0.0112</v>
       </c>
       <c r="I570" t="n">
-        <v>91.966838</v>
+        <v>9196.683800000001</v>
       </c>
     </row>
     <row r="571">
@@ -19322,7 +19322,7 @@
         <v>0.0103</v>
       </c>
       <c r="I591" t="n">
-        <v>84.048225</v>
+        <v>8404.8225</v>
       </c>
     </row>
     <row r="592">
@@ -19355,7 +19355,7 @@
         <v>0.0102</v>
       </c>
       <c r="I592" t="n">
-        <v>83.742503</v>
+        <v>8374.2503</v>
       </c>
     </row>
     <row r="593">
@@ -19388,7 +19388,7 @@
         <v>0.0103</v>
       </c>
       <c r="I593" t="n">
-        <v>83.00784299999999</v>
+        <v>8300.784299999999</v>
       </c>
     </row>
     <row r="594">
@@ -19421,7 +19421,7 @@
         <v>0.0117</v>
       </c>
       <c r="I594" t="n">
-        <v>83.92501799999999</v>
+        <v>8392.5018</v>
       </c>
     </row>
     <row r="595">
@@ -19454,7 +19454,7 @@
         <v>0.0107</v>
       </c>
       <c r="I595" t="n">
-        <v>85.166286</v>
+        <v>8516.6286</v>
       </c>
     </row>
     <row r="596">
@@ -19487,7 +19487,7 @@
         <v>0.0102</v>
       </c>
       <c r="I596" t="n">
-        <v>86.215993</v>
+        <v>8621.5993</v>
       </c>
     </row>
     <row r="597">
@@ -19520,7 +19520,7 @@
         <v>0.0102</v>
       </c>
       <c r="I597" t="n">
-        <v>85.532411</v>
+        <v>8553.241099999999</v>
       </c>
     </row>
     <row r="598">
@@ -19553,7 +19553,7 @@
         <v>0.0112</v>
       </c>
       <c r="I598" t="n">
-        <v>85.36599200000001</v>
+        <v>8536.599200000001</v>
       </c>
     </row>
     <row r="599">
@@ -19586,7 +19586,7 @@
         <v>0.0112</v>
       </c>
       <c r="I599" t="n">
-        <v>85.365269</v>
+        <v>8536.526900000001</v>
       </c>
     </row>
     <row r="600">
@@ -19619,7 +19619,7 @@
         <v>0.0092</v>
       </c>
       <c r="I600" t="n">
-        <v>86.45939199999999</v>
+        <v>8645.939200000001</v>
       </c>
     </row>
     <row r="601">
@@ -19652,7 +19652,7 @@
         <v>0.0117</v>
       </c>
       <c r="I601" t="n">
-        <v>88.76237999999999</v>
+        <v>8876.237999999999</v>
       </c>
     </row>
     <row r="602">
@@ -19685,7 +19685,7 @@
         <v>0.0092</v>
       </c>
       <c r="I602" t="n">
-        <v>90.555673</v>
+        <v>9055.567300000001</v>
       </c>
     </row>
     <row r="603">
@@ -19718,7 +19718,7 @@
         <v>0.0112</v>
       </c>
       <c r="I603" t="n">
-        <v>91.966838</v>
+        <v>9196.683800000001</v>
       </c>
     </row>
     <row r="604">
@@ -20340,7 +20340,7 @@
         <v>0.0103</v>
       </c>
       <c r="I623" t="n">
-        <v>84.048225</v>
+        <v>8404.8225</v>
       </c>
     </row>
     <row r="624">
@@ -20373,7 +20373,7 @@
         <v>0.0102</v>
       </c>
       <c r="I624" t="n">
-        <v>83.742503</v>
+        <v>8374.2503</v>
       </c>
     </row>
     <row r="625">
@@ -20406,7 +20406,7 @@
         <v>0.0103</v>
       </c>
       <c r="I625" t="n">
-        <v>83.00784299999999</v>
+        <v>8300.784299999999</v>
       </c>
     </row>
     <row r="626">
@@ -20439,7 +20439,7 @@
         <v>0.0117</v>
       </c>
       <c r="I626" t="n">
-        <v>83.92501799999999</v>
+        <v>8392.5018</v>
       </c>
     </row>
     <row r="627">
@@ -20472,7 +20472,7 @@
         <v>0.0107</v>
       </c>
       <c r="I627" t="n">
-        <v>85.166286</v>
+        <v>8516.6286</v>
       </c>
     </row>
     <row r="628">
@@ -20505,7 +20505,7 @@
         <v>0.0102</v>
       </c>
       <c r="I628" t="n">
-        <v>86.215993</v>
+        <v>8621.5993</v>
       </c>
     </row>
     <row r="629">
@@ -20538,7 +20538,7 @@
         <v>0.0102</v>
       </c>
       <c r="I629" t="n">
-        <v>85.532411</v>
+        <v>8553.241099999999</v>
       </c>
     </row>
     <row r="630">
@@ -20571,7 +20571,7 @@
         <v>0.0112</v>
       </c>
       <c r="I630" t="n">
-        <v>85.36599200000001</v>
+        <v>8536.599200000001</v>
       </c>
     </row>
     <row r="631">
@@ -20604,7 +20604,7 @@
         <v>0.0112</v>
       </c>
       <c r="I631" t="n">
-        <v>85.365269</v>
+        <v>8536.526900000001</v>
       </c>
     </row>
     <row r="632">
@@ -20637,7 +20637,7 @@
         <v>0.0092</v>
       </c>
       <c r="I632" t="n">
-        <v>86.45939199999999</v>
+        <v>8645.939200000001</v>
       </c>
     </row>
     <row r="633">
@@ -20670,7 +20670,7 @@
         <v>0.0117</v>
       </c>
       <c r="I633" t="n">
-        <v>88.76237999999999</v>
+        <v>8876.237999999999</v>
       </c>
     </row>
     <row r="634">
@@ -20703,7 +20703,7 @@
         <v>0.0092</v>
       </c>
       <c r="I634" t="n">
-        <v>90.555673</v>
+        <v>9055.567300000001</v>
       </c>
     </row>
     <row r="635">
@@ -20736,7 +20736,7 @@
         <v>0.0112</v>
       </c>
       <c r="I635" t="n">
-        <v>91.966838</v>
+        <v>9196.683800000001</v>
       </c>
     </row>
     <row r="636">
@@ -21358,7 +21358,7 @@
         <v>0.0083</v>
       </c>
       <c r="I655" t="n">
-        <v>83.244962</v>
+        <v>8324.4962</v>
       </c>
     </row>
     <row r="656">
@@ -21391,7 +21391,7 @@
         <v>0.0103</v>
       </c>
       <c r="I656" t="n">
-        <v>84.048225</v>
+        <v>8404.8225</v>
       </c>
     </row>
     <row r="657">
@@ -21424,7 +21424,7 @@
         <v>0.0102</v>
       </c>
       <c r="I657" t="n">
-        <v>83.742503</v>
+        <v>8374.2503</v>
       </c>
     </row>
     <row r="658">
@@ -21457,7 +21457,7 @@
         <v>0.0103</v>
       </c>
       <c r="I658" t="n">
-        <v>83.00784299999999</v>
+        <v>8300.784299999999</v>
       </c>
     </row>
     <row r="659">
@@ -21490,7 +21490,7 @@
         <v>0.0117</v>
       </c>
       <c r="I659" t="n">
-        <v>83.92501799999999</v>
+        <v>8392.5018</v>
       </c>
     </row>
     <row r="660">
@@ -21523,7 +21523,7 @@
         <v>0.0107</v>
       </c>
       <c r="I660" t="n">
-        <v>85.166286</v>
+        <v>8516.6286</v>
       </c>
     </row>
     <row r="661">
@@ -21556,7 +21556,7 @@
         <v>0.0102</v>
       </c>
       <c r="I661" t="n">
-        <v>86.215993</v>
+        <v>8621.5993</v>
       </c>
     </row>
     <row r="662">
@@ -21589,7 +21589,7 @@
         <v>0.0102</v>
       </c>
       <c r="I662" t="n">
-        <v>85.532411</v>
+        <v>8553.241099999999</v>
       </c>
     </row>
     <row r="663">
@@ -21622,7 +21622,7 @@
         <v>0.0112</v>
       </c>
       <c r="I663" t="n">
-        <v>85.36599200000001</v>
+        <v>8536.599200000001</v>
       </c>
     </row>
     <row r="664">
@@ -21655,7 +21655,7 @@
         <v>0.0112</v>
       </c>
       <c r="I664" t="n">
-        <v>85.365269</v>
+        <v>8536.526900000001</v>
       </c>
     </row>
     <row r="665">
@@ -21688,7 +21688,7 @@
         <v>0.0092</v>
       </c>
       <c r="I665" t="n">
-        <v>86.45939199999999</v>
+        <v>8645.939200000001</v>
       </c>
     </row>
     <row r="666">
@@ -21721,7 +21721,7 @@
         <v>0.0117</v>
       </c>
       <c r="I666" t="n">
-        <v>88.76237999999999</v>
+        <v>8876.237999999999</v>
       </c>
     </row>
     <row r="667">
@@ -21754,7 +21754,7 @@
         <v>0.0092</v>
       </c>
       <c r="I667" t="n">
-        <v>90.555673</v>
+        <v>9055.567300000001</v>
       </c>
     </row>
     <row r="668">
@@ -21787,7 +21787,7 @@
         <v>0.0112</v>
       </c>
       <c r="I668" t="n">
-        <v>91.966838</v>
+        <v>9196.683800000001</v>
       </c>
     </row>
     <row r="669">
@@ -22347,7 +22347,7 @@
         <v>0.009299999999999999</v>
       </c>
       <c r="I686" t="n">
-        <v>82.558853</v>
+        <v>8255.8853</v>
       </c>
     </row>
     <row r="687">
@@ -22380,7 +22380,7 @@
         <v>0.0083</v>
       </c>
       <c r="I687" t="n">
-        <v>83.244962</v>
+        <v>8324.4962</v>
       </c>
     </row>
     <row r="688">
@@ -22413,7 +22413,7 @@
         <v>0.0103</v>
       </c>
       <c r="I688" t="n">
-        <v>84.048225</v>
+        <v>8404.8225</v>
       </c>
     </row>
     <row r="689">
@@ -22446,7 +22446,7 @@
         <v>0.0102</v>
       </c>
       <c r="I689" t="n">
-        <v>83.742503</v>
+        <v>8374.2503</v>
       </c>
     </row>
     <row r="690">
@@ -22479,7 +22479,7 @@
         <v>0.0103</v>
       </c>
       <c r="I690" t="n">
-        <v>83.00784299999999</v>
+        <v>8300.784299999999</v>
       </c>
     </row>
     <row r="691">
@@ -22512,7 +22512,7 @@
         <v>0.0117</v>
       </c>
       <c r="I691" t="n">
-        <v>83.92501799999999</v>
+        <v>8392.5018</v>
       </c>
     </row>
     <row r="692">
@@ -22545,7 +22545,7 @@
         <v>0.0107</v>
       </c>
       <c r="I692" t="n">
-        <v>85.166286</v>
+        <v>8516.6286</v>
       </c>
     </row>
     <row r="693">
@@ -22578,7 +22578,7 @@
         <v>0.0102</v>
       </c>
       <c r="I693" t="n">
-        <v>86.215993</v>
+        <v>8621.5993</v>
       </c>
     </row>
     <row r="694">
@@ -22611,7 +22611,7 @@
         <v>0.0102</v>
       </c>
       <c r="I694" t="n">
-        <v>85.532411</v>
+        <v>8553.241099999999</v>
       </c>
     </row>
     <row r="695">
@@ -22644,7 +22644,7 @@
         <v>0.0112</v>
       </c>
       <c r="I695" t="n">
-        <v>85.36599200000001</v>
+        <v>8536.599200000001</v>
       </c>
     </row>
     <row r="696">
@@ -22677,7 +22677,7 @@
         <v>0.0112</v>
       </c>
       <c r="I696" t="n">
-        <v>85.365269</v>
+        <v>8536.526900000001</v>
       </c>
     </row>
     <row r="697">
@@ -22710,7 +22710,7 @@
         <v>0.0092</v>
       </c>
       <c r="I697" t="n">
-        <v>86.45939199999999</v>
+        <v>8645.939200000001</v>
       </c>
     </row>
     <row r="698">
@@ -22743,7 +22743,7 @@
         <v>0.0117</v>
       </c>
       <c r="I698" t="n">
-        <v>88.76237999999999</v>
+        <v>8876.237999999999</v>
       </c>
     </row>
     <row r="699">
@@ -22776,7 +22776,7 @@
         <v>0.0092</v>
       </c>
       <c r="I699" t="n">
-        <v>90.555673</v>
+        <v>9055.567300000001</v>
       </c>
     </row>
     <row r="700">
@@ -22809,7 +22809,7 @@
         <v>0.0112</v>
       </c>
       <c r="I700" t="n">
-        <v>91.966838</v>
+        <v>9196.683800000001</v>
       </c>
     </row>
     <row r="701">
